--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/21.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/21.xlsx
@@ -426,13 +426,13 @@
         <v>-8.500219021093468</v>
       </c>
       <c r="E2">
-        <v>-13.52219754562358</v>
+        <v>-21.56406999824895</v>
       </c>
       <c r="F2">
-        <v>-3.100960384931345</v>
+        <v>-2.84056309186132</v>
       </c>
       <c r="G2">
-        <v>-10.90188252349488</v>
+        <v>-14.98033392969156</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.591407901193735</v>
       </c>
       <c r="E3">
-        <v>-14.57391299153498</v>
+        <v>-22.03936051619801</v>
       </c>
       <c r="F3">
-        <v>-2.947260126811508</v>
+        <v>-2.813991550681721</v>
       </c>
       <c r="G3">
-        <v>-10.61161058006604</v>
+        <v>-14.33267369784347</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.598997233006642</v>
       </c>
       <c r="E4">
-        <v>-15.43620236970553</v>
+        <v>-22.14056738179543</v>
       </c>
       <c r="F4">
-        <v>-2.524837483223511</v>
+        <v>-2.787205462344796</v>
       </c>
       <c r="G4">
-        <v>-10.33082666015275</v>
+        <v>-14.0649995382657</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.505922546237748</v>
       </c>
       <c r="E5">
-        <v>-15.58739453139962</v>
+        <v>-23.0881777387445</v>
       </c>
       <c r="F5">
-        <v>-2.730153314211786</v>
+        <v>-2.730375316675736</v>
       </c>
       <c r="G5">
-        <v>-10.51949465043582</v>
+        <v>-14.16759996561879</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.311557879708005</v>
       </c>
       <c r="E6">
-        <v>-16.5201333797075</v>
+        <v>-22.46427628928573</v>
       </c>
       <c r="F6">
-        <v>-2.631943731670682</v>
+        <v>-2.55500082546165</v>
       </c>
       <c r="G6">
-        <v>-10.33430935406007</v>
+        <v>-14.45212149144592</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.004381555146736</v>
       </c>
       <c r="E7">
-        <v>-16.66569664821006</v>
+        <v>-23.46263725443876</v>
       </c>
       <c r="F7">
-        <v>-2.328506125086001</v>
+        <v>-2.499847295415856</v>
       </c>
       <c r="G7">
-        <v>-9.642557621447196</v>
+        <v>-14.18501509042813</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.590969357917402</v>
       </c>
       <c r="E8">
-        <v>-17.31384354750589</v>
+        <v>-24.18927166523554</v>
       </c>
       <c r="F8">
-        <v>-2.272744573366552</v>
+        <v>-2.510487674704815</v>
       </c>
       <c r="G8">
-        <v>-9.381987892596699</v>
+        <v>-13.84985546003231</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.068155260933148</v>
       </c>
       <c r="E9">
-        <v>-17.67370326299943</v>
+        <v>-24.22336201756528</v>
       </c>
       <c r="F9">
-        <v>-2.421391790329312</v>
+        <v>-2.461753163663315</v>
       </c>
       <c r="G9">
-        <v>-9.18484821627864</v>
+        <v>-13.84794858580169</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.430764720581729</v>
       </c>
       <c r="E10">
-        <v>-18.63732630403962</v>
+        <v>-25.15902173160811</v>
       </c>
       <c r="F10">
-        <v>-2.286565883482262</v>
+        <v>-2.476793002228543</v>
       </c>
       <c r="G10">
-        <v>-9.124553250371894</v>
+        <v>-13.7134361547228</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.68912882805283</v>
       </c>
       <c r="E11">
-        <v>-19.09583882579025</v>
+        <v>-25.02572609919233</v>
       </c>
       <c r="F11">
-        <v>-2.286366246938187</v>
+        <v>-2.433905108316001</v>
       </c>
       <c r="G11">
-        <v>-8.096546096789709</v>
+        <v>-13.43875357023839</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.839414755441987</v>
       </c>
       <c r="E12">
-        <v>-19.73663148329763</v>
+        <v>-26.40535287647315</v>
       </c>
       <c r="F12">
-        <v>-2.093856975997193</v>
+        <v>-2.021578606633325</v>
       </c>
       <c r="G12">
-        <v>-7.493507052992687</v>
+        <v>-12.99853708769934</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.876421607821894</v>
       </c>
       <c r="E13">
-        <v>-20.01979243452325</v>
+        <v>-27.1801430798675</v>
       </c>
       <c r="F13">
-        <v>-2.01686353937659</v>
+        <v>-2.082624314015232</v>
       </c>
       <c r="G13">
-        <v>-8.399477566360719</v>
+        <v>-12.889593655093</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.816412686426919</v>
       </c>
       <c r="E14">
-        <v>-21.07681978044565</v>
+        <v>-27.96225582573224</v>
       </c>
       <c r="F14">
-        <v>-2.104542087125904</v>
+        <v>-1.843371927269067</v>
       </c>
       <c r="G14">
-        <v>-7.44452422119363</v>
+        <v>-12.24203439488386</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.663331919142525</v>
       </c>
       <c r="E15">
-        <v>-22.15110514081128</v>
+        <v>-28.70567728967545</v>
       </c>
       <c r="F15">
-        <v>-1.980093138733723</v>
+        <v>-1.833076977187075</v>
       </c>
       <c r="G15">
-        <v>-6.460395038188945</v>
+        <v>-11.902571055287</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.430828444028535</v>
       </c>
       <c r="E16">
-        <v>-22.75013168254591</v>
+        <v>-29.03547699470607</v>
       </c>
       <c r="F16">
-        <v>-1.586467859536648</v>
+        <v>-1.74440687365661</v>
       </c>
       <c r="G16">
-        <v>-6.483343739867173</v>
+        <v>-11.74888228917187</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.8404014312075173</v>
       </c>
       <c r="E17">
-        <v>-23.62464341206316</v>
+        <v>-29.86734408449309</v>
       </c>
       <c r="F17">
-        <v>-1.550238382807809</v>
+        <v>-1.355551333964855</v>
       </c>
       <c r="G17">
-        <v>-6.42853103737346</v>
+        <v>-11.67973161394757</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.121255949163582</v>
       </c>
       <c r="E18">
-        <v>-24.33556854652734</v>
+        <v>-30.09512406284191</v>
       </c>
       <c r="F18">
-        <v>-1.418474121881506</v>
+        <v>-1.125416787221305</v>
       </c>
       <c r="G18">
-        <v>-5.085465885909914</v>
+        <v>-11.02014514179426</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.374196387266089</v>
       </c>
       <c r="E19">
-        <v>-25.05139348986781</v>
+        <v>-31.17280125023928</v>
       </c>
       <c r="F19">
-        <v>-1.303333537994583</v>
+        <v>-1.125578318864851</v>
       </c>
       <c r="G19">
-        <v>-4.738831904674986</v>
+        <v>-10.73019101073719</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.546650276361542</v>
       </c>
       <c r="E20">
-        <v>-25.8696661006838</v>
+        <v>-32.42896824064898</v>
       </c>
       <c r="F20">
-        <v>-0.940290754941463</v>
+        <v>-1.158708044772414</v>
       </c>
       <c r="G20">
-        <v>-3.96583276343732</v>
+        <v>-9.989075733588249</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.608031318264497</v>
       </c>
       <c r="E21">
-        <v>-26.46098970813139</v>
+        <v>-32.0098602354761</v>
       </c>
       <c r="F21">
-        <v>-0.8130518651366533</v>
+        <v>-0.8400566424679172</v>
       </c>
       <c r="G21">
-        <v>-4.683996028362498</v>
+        <v>-9.96836165014903</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.530139063759181</v>
       </c>
       <c r="E22">
-        <v>-25.8384332154529</v>
+        <v>-32.92393044968735</v>
       </c>
       <c r="F22">
-        <v>-0.8471897141734237</v>
+        <v>-0.8359264025975589</v>
       </c>
       <c r="G22">
-        <v>-4.434317994336204</v>
+        <v>-9.961028791779544</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.284121471296156</v>
       </c>
       <c r="E23">
-        <v>-27.09998456145772</v>
+        <v>-33.10029866262709</v>
       </c>
       <c r="F23">
-        <v>-0.6121711132229676</v>
+        <v>-0.8597129725689466</v>
       </c>
       <c r="G23">
-        <v>-4.429097264020773</v>
+        <v>-9.427392024667805</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.865264673264658</v>
       </c>
       <c r="E24">
-        <v>-27.84518571568595</v>
+        <v>-33.9358157024643</v>
       </c>
       <c r="F24">
-        <v>-0.7022519264403998</v>
+        <v>-0.5461485744850414</v>
       </c>
       <c r="G24">
-        <v>-4.203321368788018</v>
+        <v>-9.165961553977098</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.272754612435243</v>
       </c>
       <c r="E25">
-        <v>-27.97051123384822</v>
+        <v>-33.89682554125825</v>
       </c>
       <c r="F25">
-        <v>-0.6273393487356294</v>
+        <v>-0.5105602541259691</v>
       </c>
       <c r="G25">
-        <v>-3.962823477542123</v>
+        <v>-9.899926052761217</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.509134719211646</v>
       </c>
       <c r="E26">
-        <v>-27.68010925268434</v>
+        <v>-33.75549639595287</v>
       </c>
       <c r="F26">
-        <v>-0.3114638055979135</v>
+        <v>-0.4601632097070499</v>
       </c>
       <c r="G26">
-        <v>-4.013345713016941</v>
+        <v>-9.536851902378267</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.591967135265586</v>
       </c>
       <c r="E27">
-        <v>-28.04975500050845</v>
+        <v>-33.66576468349088</v>
       </c>
       <c r="F27">
-        <v>-0.3379674206504836</v>
+        <v>-0.5751298364393849</v>
       </c>
       <c r="G27">
-        <v>-4.410293365357713</v>
+        <v>-10.23854851379111</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.537476807660902</v>
       </c>
       <c r="E28">
-        <v>-28.00400835608296</v>
+        <v>-35.21205062543899</v>
       </c>
       <c r="F28">
-        <v>-0.4236164682629385</v>
+        <v>-0.4906479584974745</v>
       </c>
       <c r="G28">
-        <v>-4.526470339967357</v>
+        <v>-10.31021851417079</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.364278169600366</v>
       </c>
       <c r="E29">
-        <v>-27.28864984556528</v>
+        <v>-34.72627442592518</v>
       </c>
       <c r="F29">
-        <v>-0.07422932184496865</v>
+        <v>-0.5708720279889954</v>
       </c>
       <c r="G29">
-        <v>-4.625614557777451</v>
+        <v>-9.666098910776952</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.094377775641327</v>
       </c>
       <c r="E30">
-        <v>-26.98624740828107</v>
+        <v>-34.48564716681661</v>
       </c>
       <c r="F30">
-        <v>-0.1226954418479621</v>
+        <v>-0.3634405466539712</v>
       </c>
       <c r="G30">
-        <v>-4.588582795375163</v>
+        <v>-9.793402628944087</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.744735605919756</v>
       </c>
       <c r="E31">
-        <v>-27.58611624618113</v>
+        <v>-34.1334790644251</v>
       </c>
       <c r="F31">
-        <v>-0.2052770449678504</v>
+        <v>-0.5834101969977687</v>
       </c>
       <c r="G31">
-        <v>-4.554603355960083</v>
+        <v>-10.40019583138264</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.334372958875046</v>
       </c>
       <c r="E32">
-        <v>-26.57236752635004</v>
+        <v>-33.25334523442732</v>
       </c>
       <c r="F32">
-        <v>-0.3548586603609684</v>
+        <v>-0.5701579752877822</v>
       </c>
       <c r="G32">
-        <v>-4.89802279747638</v>
+        <v>-10.08095992503072</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.876130374145894</v>
       </c>
       <c r="E33">
-        <v>-26.48821942233951</v>
+        <v>-33.8001471496685</v>
       </c>
       <c r="F33">
-        <v>-0.5676355965462577</v>
+        <v>-0.7936374183172413</v>
       </c>
       <c r="G33">
-        <v>-4.909735507594322</v>
+        <v>-9.982246078140733</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.378180740547252</v>
       </c>
       <c r="E34">
-        <v>-26.09239456627706</v>
+        <v>-32.97920726766198</v>
       </c>
       <c r="F34">
-        <v>-0.4381319502621943</v>
+        <v>-0.595742102523245</v>
       </c>
       <c r="G34">
-        <v>-5.425693961526354</v>
+        <v>-10.45915664743706</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.852240816889752</v>
       </c>
       <c r="E35">
-        <v>-26.12614981153023</v>
+        <v>-32.2653205111968</v>
       </c>
       <c r="F35">
-        <v>-0.5691523372607836</v>
+        <v>-0.4872276294913154</v>
       </c>
       <c r="G35">
-        <v>-5.183924820793379</v>
+        <v>-10.1268672600238</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.29945142405449</v>
       </c>
       <c r="E36">
-        <v>-24.85648796857767</v>
+        <v>-32.42948675092286</v>
       </c>
       <c r="F36">
-        <v>-0.384000625591455</v>
+        <v>-0.5914950628490919</v>
       </c>
       <c r="G36">
-        <v>-5.252320691634721</v>
+        <v>-9.954612954524437</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.720080699346125</v>
       </c>
       <c r="E37">
-        <v>-24.63305758951322</v>
+        <v>-32.16865796926607</v>
       </c>
       <c r="F37">
-        <v>-0.7698491916110479</v>
+        <v>-0.3508609592750579</v>
       </c>
       <c r="G37">
-        <v>-5.697003100106246</v>
+        <v>-10.65388624660253</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.120368064400428</v>
       </c>
       <c r="E38">
-        <v>-24.78585283100603</v>
+        <v>-31.11983848248257</v>
       </c>
       <c r="F38">
-        <v>-0.632604451947823</v>
+        <v>-0.4198308292321448</v>
       </c>
       <c r="G38">
-        <v>-6.455687442432102</v>
+        <v>-10.65970949620611</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.49564074087267</v>
       </c>
       <c r="E39">
-        <v>-23.68947757443098</v>
+        <v>-30.58776995742535</v>
       </c>
       <c r="F39">
-        <v>-0.4460668816136107</v>
+        <v>-0.5691589642000061</v>
       </c>
       <c r="G39">
-        <v>-6.016364807188658</v>
+        <v>-10.44475246379569</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.845326545821987</v>
       </c>
       <c r="E40">
-        <v>-22.8146533802072</v>
+        <v>-31.02007393585659</v>
       </c>
       <c r="F40">
-        <v>-0.5533702815026474</v>
+        <v>-0.396981971160726</v>
       </c>
       <c r="G40">
-        <v>-5.989698362869829</v>
+        <v>-10.26386425552992</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.175248040745497</v>
       </c>
       <c r="E41">
-        <v>-22.71960523926021</v>
+        <v>-29.76975320539079</v>
       </c>
       <c r="F41">
-        <v>-0.2829074961212061</v>
+        <v>-0.4171883372172144</v>
       </c>
       <c r="G41">
-        <v>-6.143264638800002</v>
+        <v>-10.4680620149377</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.480264943778224</v>
       </c>
       <c r="E42">
-        <v>-21.43202422465929</v>
+        <v>-29.12998171877214</v>
       </c>
       <c r="F42">
-        <v>-0.4513866570743891</v>
+        <v>-0.4562607708724615</v>
       </c>
       <c r="G42">
-        <v>-6.341615974785435</v>
+        <v>-10.23636686428073</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.7625826748726461</v>
       </c>
       <c r="E43">
-        <v>-21.80091371732412</v>
+        <v>-28.16491409452351</v>
       </c>
       <c r="F43">
-        <v>-0.5247435607967021</v>
+        <v>-0.05446613234897805</v>
       </c>
       <c r="G43">
-        <v>-5.955149509621995</v>
+        <v>-10.27247498447756</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.02962086408258099</v>
       </c>
       <c r="E44">
-        <v>-20.83208745964912</v>
+        <v>-28.39800370864631</v>
       </c>
       <c r="F44">
-        <v>-0.2952650810361691</v>
+        <v>-0.2930583102751113</v>
       </c>
       <c r="G44">
-        <v>-6.451549260508012</v>
+        <v>-10.46194743732667</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7205505252495438</v>
       </c>
       <c r="E45">
-        <v>-20.56856197172076</v>
+        <v>-26.73062410749609</v>
       </c>
       <c r="F45">
-        <v>-0.4796828591866175</v>
+        <v>-0.2924130120683304</v>
       </c>
       <c r="G45">
-        <v>-5.700452688558165</v>
+        <v>-10.7449858387522</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.479351277829867</v>
       </c>
       <c r="E46">
-        <v>-19.15663358934322</v>
+        <v>-27.83885038054922</v>
       </c>
       <c r="F46">
-        <v>-0.4932755398991546</v>
+        <v>-0.2001229429876319</v>
       </c>
       <c r="G46">
-        <v>-5.911917095424652</v>
+        <v>-10.9760850912121</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.233451220963737</v>
       </c>
       <c r="E47">
-        <v>-19.02270397056637</v>
+        <v>-27.23498742857439</v>
       </c>
       <c r="F47">
-        <v>-0.3650740871722919</v>
+        <v>-0.2414584763873273</v>
       </c>
       <c r="G47">
-        <v>-6.202298286856285</v>
+        <v>-10.51338669391586</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.977407795957456</v>
       </c>
       <c r="E48">
-        <v>-17.73571618606046</v>
+        <v>-26.91998677660084</v>
       </c>
       <c r="F48">
-        <v>-0.5605928168876564</v>
+        <v>-0.1488453440195369</v>
       </c>
       <c r="G48">
-        <v>-6.414295691554594</v>
+        <v>-10.24104797567326</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.695991282139846</v>
       </c>
       <c r="E49">
-        <v>-17.98491358222856</v>
+        <v>-25.41975315107373</v>
       </c>
       <c r="F49">
-        <v>-0.6055806221662947</v>
+        <v>-0.2077488932978042</v>
       </c>
       <c r="G49">
-        <v>-6.34027520384203</v>
+        <v>-10.71475724743311</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.373471823324579</v>
       </c>
       <c r="E50">
-        <v>-17.73386404019133</v>
+        <v>-24.79117378796504</v>
       </c>
       <c r="F50">
-        <v>-0.4960812202924365</v>
+        <v>-0.3139605049499511</v>
       </c>
       <c r="G50">
-        <v>-6.557966746867885</v>
+        <v>-10.78696024564462</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.00156426121825</v>
       </c>
       <c r="E51">
-        <v>-16.97899912243073</v>
+        <v>-25.77076875683029</v>
       </c>
       <c r="F51">
-        <v>-0.5972812091576465</v>
+        <v>-0.2163589440825022</v>
       </c>
       <c r="G51">
-        <v>-6.371622759553389</v>
+        <v>-11.02310145896083</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.564450161136197</v>
       </c>
       <c r="E52">
-        <v>-16.13117369024068</v>
+        <v>-24.18925355133951</v>
       </c>
       <c r="F52">
-        <v>-0.390268053361036</v>
+        <v>-0.2304718395239974</v>
       </c>
       <c r="G52">
-        <v>-6.355814904603369</v>
+        <v>-10.37352607651827</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.047468046492519</v>
       </c>
       <c r="E53">
-        <v>-16.0749209861174</v>
+        <v>-23.52682384502348</v>
       </c>
       <c r="F53">
-        <v>-0.6887967547167274</v>
+        <v>-0.1301755994952417</v>
       </c>
       <c r="G53">
-        <v>-6.859944779323585</v>
+        <v>-10.72721483029739</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.441595391527226</v>
       </c>
       <c r="E54">
-        <v>-15.2104217126311</v>
+        <v>-23.40191947494392</v>
       </c>
       <c r="F54">
-        <v>-0.6877505266869917</v>
+        <v>0.1056365774270964</v>
       </c>
       <c r="G54">
-        <v>-6.064728566971871</v>
+        <v>-10.70299156858654</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.734228730977769</v>
       </c>
       <c r="E55">
-        <v>-15.25005944562024</v>
+        <v>-23.47351917747919</v>
       </c>
       <c r="F55">
-        <v>-0.7482089215803136</v>
+        <v>-0.3171290102656593</v>
       </c>
       <c r="G55">
-        <v>-6.514128502836856</v>
+        <v>-10.88019845021265</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.918437721208939</v>
       </c>
       <c r="E56">
-        <v>-14.43603001494944</v>
+        <v>-22.23962775071322</v>
       </c>
       <c r="F56">
-        <v>-0.5146308515433258</v>
+        <v>-0.3248709320122234</v>
       </c>
       <c r="G56">
-        <v>-5.764058200004183</v>
+        <v>-10.6428654405023</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.993206350875633</v>
       </c>
       <c r="E57">
-        <v>-14.32869612401963</v>
+        <v>-22.90520927493858</v>
       </c>
       <c r="F57">
-        <v>-0.6229208370090967</v>
+        <v>-0.1164826863269658</v>
       </c>
       <c r="G57">
-        <v>-7.15653986473243</v>
+        <v>-10.9483923777761</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.959254916520388</v>
       </c>
       <c r="E58">
-        <v>-13.58826345292148</v>
+        <v>-22.06599247183711</v>
       </c>
       <c r="F58">
-        <v>-0.9779499938075341</v>
+        <v>-0.4241756162598282</v>
       </c>
       <c r="G58">
-        <v>-6.914068888345129</v>
+        <v>-11.46441704261892</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.82394341766447</v>
       </c>
       <c r="E59">
-        <v>-13.68292667357782</v>
+        <v>-21.70551235540453</v>
       </c>
       <c r="F59">
-        <v>-1.161271013516676</v>
+        <v>-0.2027952562290631</v>
       </c>
       <c r="G59">
-        <v>-7.240823043616735</v>
+        <v>-10.9025247693295</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.597257512830338</v>
       </c>
       <c r="E60">
-        <v>-12.70329094844651</v>
+        <v>-20.80872506224355</v>
       </c>
       <c r="F60">
-        <v>-0.9722466842392595</v>
+        <v>-0.6238088468648979</v>
       </c>
       <c r="G60">
-        <v>-6.918677167735795</v>
+        <v>-11.93606053396226</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.292289791781704</v>
       </c>
       <c r="E61">
-        <v>-12.98434615925856</v>
+        <v>-20.9473778794104</v>
       </c>
       <c r="F61">
-        <v>-1.083103780286306</v>
+        <v>-0.4570005029631614</v>
       </c>
       <c r="G61">
-        <v>-6.948346276858743</v>
+        <v>-11.61661606324137</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.926975860369541</v>
       </c>
       <c r="E62">
-        <v>-12.52332939138169</v>
+        <v>-21.05538198449334</v>
       </c>
       <c r="F62">
-        <v>-0.9960547917631201</v>
+        <v>-0.5872240005202577</v>
       </c>
       <c r="G62">
-        <v>-7.519759679119107</v>
+        <v>-11.22570684596423</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.517247536921627</v>
       </c>
       <c r="E63">
-        <v>-12.23149188395737</v>
+        <v>-20.78013680583312</v>
       </c>
       <c r="F63">
-        <v>-1.073087990019057</v>
+        <v>-0.6270013748352872</v>
       </c>
       <c r="G63">
-        <v>-7.72942645975777</v>
+        <v>-11.73751056524447</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.081409847331144</v>
       </c>
       <c r="E64">
-        <v>-12.10249830184889</v>
+        <v>-19.89828441994944</v>
       </c>
       <c r="F64">
-        <v>-1.008679110981785</v>
+        <v>-0.7604969236334415</v>
       </c>
       <c r="G64">
-        <v>-7.262639538720532</v>
+        <v>-11.82945765705219</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.638574770391343</v>
       </c>
       <c r="E65">
-        <v>-12.22166509536073</v>
+        <v>-20.82512719509933</v>
       </c>
       <c r="F65">
-        <v>-1.254888127176659</v>
+        <v>-0.7871239654290287</v>
       </c>
       <c r="G65">
-        <v>-7.409541686480152</v>
+        <v>-12.05005585906153</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.201359439541264</v>
       </c>
       <c r="E66">
-        <v>-11.08462867067081</v>
+        <v>-19.78823797308904</v>
       </c>
       <c r="F66">
-        <v>-1.192858319320227</v>
+        <v>-0.7202805145949283</v>
       </c>
       <c r="G66">
-        <v>-7.321501038408774</v>
+        <v>-11.72520195692946</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.784090264836185</v>
       </c>
       <c r="E67">
-        <v>-11.43061314180484</v>
+        <v>-20.05056794387938</v>
       </c>
       <c r="F67">
-        <v>-1.640708528704557</v>
+        <v>-0.8148908407708683</v>
       </c>
       <c r="G67">
-        <v>-7.311086062142227</v>
+        <v>-11.65867323377227</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.398081673649946</v>
       </c>
       <c r="E68">
-        <v>-12.11699394714744</v>
+        <v>-20.20108989142033</v>
       </c>
       <c r="F68">
-        <v>-1.716523198510976</v>
+        <v>-0.9527444304751508</v>
       </c>
       <c r="G68">
-        <v>-7.758453323046099</v>
+        <v>-12.04742397535781</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.045287651244518</v>
       </c>
       <c r="E69">
-        <v>-11.97441947148995</v>
+        <v>-19.82843723685513</v>
       </c>
       <c r="F69">
-        <v>-1.415089412673667</v>
+        <v>-1.195229106827039</v>
       </c>
       <c r="G69">
-        <v>-7.080023225683255</v>
+        <v>-11.99485582273972</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.728654810815337</v>
       </c>
       <c r="E70">
-        <v>-11.62137510937796</v>
+        <v>-19.7657178718489</v>
       </c>
       <c r="F70">
-        <v>-1.755207956221713</v>
+        <v>-1.225284761302813</v>
       </c>
       <c r="G70">
-        <v>-7.364028306406252</v>
+        <v>-11.43753541284003</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.445810778017055</v>
       </c>
       <c r="E71">
-        <v>-11.79358391894164</v>
+        <v>-19.75315588495162</v>
       </c>
       <c r="F71">
-        <v>-1.868652872035105</v>
+        <v>-1.294966198858905</v>
       </c>
       <c r="G71">
-        <v>-6.905775971769256</v>
+        <v>-11.48307858782379</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.185728339017451</v>
       </c>
       <c r="E72">
-        <v>-11.25650690163194</v>
+        <v>-20.18994984536146</v>
       </c>
       <c r="F72">
-        <v>-1.761655968085104</v>
+        <v>-1.363743887578542</v>
       </c>
       <c r="G72">
-        <v>-7.317296645573899</v>
+        <v>-11.27691436436567</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.941346411045354</v>
       </c>
       <c r="E73">
-        <v>-12.174591608051</v>
+        <v>-19.65884588526787</v>
       </c>
       <c r="F73">
-        <v>-1.865569688561886</v>
+        <v>-1.105409229341488</v>
       </c>
       <c r="G73">
-        <v>-7.063549951079842</v>
+        <v>-11.7016176305077</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.702430970671502</v>
       </c>
       <c r="E74">
-        <v>-12.04405381630589</v>
+        <v>-20.38998159922827</v>
       </c>
       <c r="F74">
-        <v>-1.809244847008533</v>
+        <v>-1.528903780348708</v>
       </c>
       <c r="G74">
-        <v>-7.271534974584553</v>
+        <v>-11.53848056742349</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.454825680319696</v>
       </c>
       <c r="E75">
-        <v>-13.17988566690977</v>
+        <v>-19.91756213380009</v>
       </c>
       <c r="F75">
-        <v>-1.892590204873803</v>
+        <v>-1.451950105363439</v>
       </c>
       <c r="G75">
-        <v>-6.511453582041125</v>
+        <v>-11.57829318807877</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.192572584617476</v>
       </c>
       <c r="E76">
-        <v>-11.90067327227503</v>
+        <v>-20.43949140555414</v>
       </c>
       <c r="F76">
-        <v>-2.026258882459142</v>
+        <v>-1.602206011822436</v>
       </c>
       <c r="G76">
-        <v>-6.036016205509772</v>
+        <v>-10.59711370114957</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.9090615936423068</v>
       </c>
       <c r="E77">
-        <v>-13.3031779002426</v>
+        <v>-20.82084325868807</v>
       </c>
       <c r="F77">
-        <v>-2.124877678497229</v>
+        <v>-1.506867550699435</v>
       </c>
       <c r="G77">
-        <v>-5.866632142992962</v>
+        <v>-10.93686174766282</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.5985132086749119</v>
       </c>
       <c r="E78">
-        <v>-13.58424216800267</v>
+        <v>-21.77177751555877</v>
       </c>
       <c r="F78">
-        <v>-1.811928757393604</v>
+        <v>-1.611154036507476</v>
       </c>
       <c r="G78">
-        <v>-6.223214313573401</v>
+        <v>-10.5325845474981</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.2654403714578901</v>
       </c>
       <c r="E79">
-        <v>-14.68014193480691</v>
+        <v>-21.10497330335133</v>
       </c>
       <c r="F79">
-        <v>-2.007430091393509</v>
+        <v>-1.88864800440388</v>
       </c>
       <c r="G79">
-        <v>-5.885677711480389</v>
+        <v>-10.66146739588746</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.08530934310907509</v>
       </c>
       <c r="E80">
-        <v>-14.9838848003974</v>
+        <v>-22.03022658412453</v>
       </c>
       <c r="F80">
-        <v>-1.96993404090579</v>
+        <v>-1.838465507142286</v>
       </c>
       <c r="G80">
-        <v>-5.794846273519405</v>
+        <v>-10.40458892531326</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.4470519339170491</v>
       </c>
       <c r="E81">
-        <v>-15.84932146800328</v>
+        <v>-21.27476843626893</v>
       </c>
       <c r="F81">
-        <v>-1.792339525052201</v>
+        <v>-1.889398505270816</v>
       </c>
       <c r="G81">
-        <v>-5.500942661633988</v>
+        <v>-10.58461639173882</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8056164101757552</v>
       </c>
       <c r="E82">
-        <v>-16.27549615686513</v>
+        <v>-23.35601433392816</v>
       </c>
       <c r="F82">
-        <v>-2.035852205350963</v>
+        <v>-2.05211388583532</v>
       </c>
       <c r="G82">
-        <v>-4.304028164092647</v>
+        <v>-9.823882821724156</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.148417485439118</v>
       </c>
       <c r="E83">
-        <v>-16.59171949682075</v>
+        <v>-23.72832282446878</v>
       </c>
       <c r="F83">
-        <v>-1.917462764510261</v>
+        <v>-2.052395530752272</v>
       </c>
       <c r="G83">
-        <v>-4.808105070084235</v>
+        <v>-9.638684283166249</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.462986590141659</v>
       </c>
       <c r="E84">
-        <v>-18.2021399519025</v>
+        <v>-24.08425635299766</v>
       </c>
       <c r="F84">
-        <v>-2.337597457331725</v>
+        <v>-1.874492862224842</v>
       </c>
       <c r="G84">
-        <v>-4.560436537200279</v>
+        <v>-9.787288051333054</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.733783150399982</v>
       </c>
       <c r="E85">
-        <v>-18.01174931919801</v>
+        <v>-25.21595823530654</v>
       </c>
       <c r="F85">
-        <v>-1.98547752685192</v>
+        <v>-2.234606538141663</v>
       </c>
       <c r="G85">
-        <v>-4.605013032886566</v>
+        <v>-9.796127207922908</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.948810327378161</v>
       </c>
       <c r="E86">
-        <v>-20.17019664174</v>
+        <v>-25.41857121935773</v>
       </c>
       <c r="F86">
-        <v>-2.218486508483184</v>
+        <v>-2.26238169715753</v>
       </c>
       <c r="G86">
-        <v>-4.383514362490549</v>
+        <v>-9.691206088146785</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.097784228098052</v>
       </c>
       <c r="E87">
-        <v>-21.41948488013206</v>
+        <v>-26.87953844676433</v>
       </c>
       <c r="F87">
-        <v>-2.092627678771438</v>
+        <v>-2.183016644662712</v>
       </c>
       <c r="G87">
-        <v>-4.244825678213861</v>
+        <v>-9.079986686322226</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.171841056368958</v>
       </c>
       <c r="E88">
-        <v>-21.87427499624838</v>
+        <v>-28.00594654295825</v>
       </c>
       <c r="F88">
-        <v>-2.491213221976476</v>
+        <v>-2.292101034467768</v>
       </c>
       <c r="G88">
-        <v>-4.291107104852872</v>
+        <v>-9.69963473708977</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.165622827405269</v>
       </c>
       <c r="E89">
-        <v>-23.46289084898319</v>
+        <v>-28.9394416464254</v>
       </c>
       <c r="F89">
-        <v>-2.656040939418119</v>
+        <v>-2.316431013455392</v>
       </c>
       <c r="G89">
-        <v>-4.404456873571978</v>
+        <v>-9.12016677753236</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.076931394314517</v>
       </c>
       <c r="E90">
-        <v>-24.93206367129168</v>
+        <v>-29.52006899826688</v>
       </c>
       <c r="F90">
-        <v>-2.492085492851624</v>
+        <v>-2.534334715496608</v>
       </c>
       <c r="G90">
-        <v>-4.369338606491389</v>
+        <v>-10.03809498138824</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.907971630805668</v>
       </c>
       <c r="E91">
-        <v>-27.37316475597044</v>
+        <v>-31.56008314008626</v>
       </c>
       <c r="F91">
-        <v>-2.18487135927758</v>
+        <v>-2.502050752707302</v>
       </c>
       <c r="G91">
-        <v>-4.404099334653736</v>
+        <v>-9.445275591670947</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.662560661396503</v>
       </c>
       <c r="E92">
-        <v>-28.55695314631554</v>
+        <v>-33.39388416101837</v>
       </c>
       <c r="F92">
-        <v>-2.788568955089804</v>
+        <v>-2.566697373189179</v>
       </c>
       <c r="G92">
-        <v>-4.432907701936474</v>
+        <v>-10.01597060554929</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.347638553230599</v>
       </c>
       <c r="E93">
-        <v>-30.57123876306035</v>
+        <v>-34.78159652863988</v>
       </c>
       <c r="F93">
-        <v>-2.18352194877842</v>
+        <v>-2.848515418928196</v>
       </c>
       <c r="G93">
-        <v>-4.079450686345107</v>
+        <v>-9.531048516047925</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.9770836337347603</v>
       </c>
       <c r="E94">
-        <v>-31.61265419484131</v>
+        <v>-36.07013984396743</v>
       </c>
       <c r="F94">
-        <v>-2.49114612421685</v>
+        <v>-2.859863223979146</v>
       </c>
       <c r="G94">
-        <v>-4.639247384308169</v>
+        <v>-9.970116239284843</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.5656180040106517</v>
       </c>
       <c r="E95">
-        <v>-34.86298226350574</v>
+        <v>-37.13395310819032</v>
       </c>
       <c r="F95">
-        <v>-2.531808194918069</v>
+        <v>-2.807299998801907</v>
       </c>
       <c r="G95">
-        <v>-4.207406581983478</v>
+        <v>-9.909549808643877</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.1269989747608011</v>
       </c>
       <c r="E96">
-        <v>-35.93146891290454</v>
+        <v>-39.60019175208565</v>
       </c>
       <c r="F96">
-        <v>-2.853474854568756</v>
+        <v>-3.187444426885822</v>
       </c>
       <c r="G96">
-        <v>-5.259305942722584</v>
+        <v>-9.715197611669884</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3134166427892797</v>
       </c>
       <c r="E97">
-        <v>-37.32316633765281</v>
+        <v>-41.03917550242201</v>
       </c>
       <c r="F97">
-        <v>-2.704696755556354</v>
+        <v>-3.391111806742525</v>
       </c>
       <c r="G97">
-        <v>-5.707000947634844</v>
+        <v>-10.72906873579938</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.7467696027922954</v>
       </c>
       <c r="E98">
-        <v>-41.31303043956186</v>
+        <v>-42.96945339785053</v>
       </c>
       <c r="F98">
-        <v>-2.902250783980397</v>
+        <v>-3.241127604791647</v>
       </c>
       <c r="G98">
-        <v>-5.484485939758271</v>
+        <v>-10.78583134961572</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.150202459728215</v>
       </c>
       <c r="E99">
-        <v>-42.31867319091923</v>
+        <v>-44.70231020467765</v>
       </c>
       <c r="F99">
-        <v>-3.173862514949521</v>
+        <v>-3.304257484558997</v>
       </c>
       <c r="G99">
-        <v>-5.936107251680107</v>
+        <v>-10.8685353982778</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.529632619772983</v>
       </c>
       <c r="E100">
-        <v>-44.43612197403278</v>
+        <v>-47.27614539099523</v>
       </c>
       <c r="F100">
-        <v>-2.90857205563116</v>
+        <v>-3.750146948300901</v>
       </c>
       <c r="G100">
-        <v>-6.076977585467175</v>
+        <v>-11.85464428751497</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.856394132652504</v>
       </c>
       <c r="E101">
-        <v>-46.49118876345366</v>
+        <v>-48.2385729148974</v>
       </c>
       <c r="F101">
-        <v>-3.052229187359456</v>
+        <v>-3.723371628740213</v>
       </c>
       <c r="G101">
-        <v>-7.268538930871514</v>
+        <v>-11.21468272931845</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.180493286094826</v>
       </c>
       <c r="E102">
-        <v>-49.06355219571875</v>
+        <v>-50.71198692585788</v>
       </c>
       <c r="F102">
-        <v>-3.07947667633974</v>
+        <v>-3.842550503715783</v>
       </c>
       <c r="G102">
-        <v>-7.093027048561512</v>
+        <v>-11.79699113694856</v>
       </c>
     </row>
   </sheetData>
